--- a/IW49_Confirmation-2026.xlsx
+++ b/IW49_Confirmation-2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1D032E-DB1E-43B7-9052-2025BE38C029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EC9C3B-BBCC-44F7-82B8-8C4520C25208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t>Order</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Finish Time</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
@@ -77,175 +74,73 @@
     <t>0010</t>
   </si>
   <si>
-    <t>0000743584</t>
-  </si>
-  <si>
-    <t>0000743587</t>
-  </si>
-  <si>
-    <t>0000743588</t>
-  </si>
-  <si>
-    <t>0000743589</t>
-  </si>
-  <si>
     <t>0000752247</t>
   </si>
   <si>
-    <t>0000752249</t>
-  </si>
-  <si>
     <t>REL NMAT PRC SETC</t>
   </si>
   <si>
     <t>222300</t>
   </si>
   <si>
-    <t>E1-N01</t>
+    <t>Duration Actual</t>
+  </si>
+  <si>
+    <t>Actual work</t>
+  </si>
+  <si>
+    <t>Oper.Work Center</t>
+  </si>
+  <si>
+    <t>Normal duration</t>
+  </si>
+  <si>
+    <t>Norm.duratn un.</t>
+  </si>
+  <si>
+    <t>System status</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Penggantian Lampu GIC Lt.1 &amp; Lt.2</t>
+  </si>
+  <si>
+    <t>Functional Loc.</t>
+  </si>
+  <si>
+    <t>A-A2-01-015-001</t>
+  </si>
+  <si>
+    <t>2210002907</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>P-22L007</t>
+  </si>
+  <si>
+    <t>MaintActivType</t>
+  </si>
+  <si>
+    <t>22F</t>
+  </si>
+  <si>
+    <t>numofwork</t>
+  </si>
+  <si>
+    <t>2020202021</t>
+  </si>
+  <si>
+    <t>2020202022</t>
+  </si>
+  <si>
+    <t>2020202023</t>
   </si>
   <si>
     <t>O1-N01</t>
-  </si>
-  <si>
-    <t>M1-N01</t>
-  </si>
-  <si>
-    <t>M1-OS1</t>
-  </si>
-  <si>
-    <t>S1-N01</t>
-  </si>
-  <si>
-    <t>Duration Actual</t>
-  </si>
-  <si>
-    <t>Actual work</t>
-  </si>
-  <si>
-    <t>2210063457</t>
-  </si>
-  <si>
-    <t>2210063458</t>
-  </si>
-  <si>
-    <t>2210063459</t>
-  </si>
-  <si>
-    <t>2210063460</t>
-  </si>
-  <si>
-    <t>2210063461</t>
-  </si>
-  <si>
-    <t>2210063462</t>
-  </si>
-  <si>
-    <t>Oper.Work Center</t>
-  </si>
-  <si>
-    <t>Normal duration</t>
-  </si>
-  <si>
-    <t>Norm.duratn un.</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>System status</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Penggantian Lampu R.Tunggu Tamu GTG Lt.2</t>
-  </si>
-  <si>
-    <t>Penggantian Lampu GIC Lt.1 &amp; Lt.2</t>
-  </si>
-  <si>
-    <t>Perbaikan Plafon GIC Lt.1</t>
-  </si>
-  <si>
-    <t>Perbaikan Kabel Flowmeter Filter WTP CDN</t>
-  </si>
-  <si>
-    <t>Kalibrasi Transmitter Level Waduk</t>
-  </si>
-  <si>
-    <t>Pengadaan Instalasi Mesin Absensi GEC</t>
-  </si>
-  <si>
-    <t>CRTD MANC NMAT PRC</t>
-  </si>
-  <si>
-    <t>Functional Loc.</t>
-  </si>
-  <si>
-    <t>A-A2-01-014</t>
-  </si>
-  <si>
-    <t>A-A2-01-015-001</t>
-  </si>
-  <si>
-    <t>A-A2-03</t>
-  </si>
-  <si>
-    <t>A-A1-03-001-001</t>
-  </si>
-  <si>
-    <t>A-A2-01-016</t>
-  </si>
-  <si>
-    <t>2210002907</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>P-22L007</t>
-  </si>
-  <si>
-    <t>I-22L003</t>
-  </si>
-  <si>
-    <t>MaintActivType</t>
-  </si>
-  <si>
-    <t>22J</t>
-  </si>
-  <si>
-    <t>22F</t>
-  </si>
-  <si>
-    <t>22D</t>
-  </si>
-  <si>
-    <t>22M</t>
-  </si>
-  <si>
-    <t>22L</t>
-  </si>
-  <si>
-    <t>Reported by</t>
-  </si>
-  <si>
-    <t>Aat Djamiatu Rohman</t>
-  </si>
-  <si>
-    <t>Moch Ridza Pahlevi</t>
-  </si>
-  <si>
-    <t>Adimas Abimanyu</t>
-  </si>
-  <si>
-    <t>Muhamad Ali Lutfi</t>
-  </si>
-  <si>
-    <t>Rihadi Achsani Takwim</t>
   </si>
 </sst>
 </file>
@@ -253,10 +148,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,12 +164,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -323,28 +212,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -691,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -715,11 +603,10 @@
     <col min="19" max="20" width="6.109375" customWidth="1"/>
     <col min="21" max="21" width="5.6640625" customWidth="1"/>
     <col min="22" max="22" width="6.109375" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" customWidth="1"/>
-    <col min="24" max="24" width="7.44140625" customWidth="1"/>
-    <col min="25" max="25" width="8.5546875" customWidth="1"/>
-    <col min="26" max="26" width="15.21875" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" customWidth="1"/>
+    <col min="23" max="23" width="7.44140625" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="15.21875" customWidth="1"/>
+    <col min="26" max="26" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
@@ -730,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -739,10 +626,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -751,10 +638,10 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>6</v>
@@ -763,10 +650,10 @@
         <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -790,60 +677,60 @@
         <v>14</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="J2" s="4">
+        <v>2</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="4">
-        <v>4</v>
-      </c>
       <c r="M2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="5">
@@ -856,59 +743,61 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
-      <c r="W2" s="3" t="s">
-        <v>72</v>
+      <c r="W2" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="AA2" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J3" s="4">
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="5">
@@ -921,61 +810,61 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>63</v>
+      <c r="W3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>61</v>
+        <v>32</v>
+      </c>
+      <c r="AA3" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="J4" s="4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0.01</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="5">
@@ -988,214 +877,21 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
-        <v>74</v>
+      <c r="W4" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>64</v>
+        <v>34</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" s="8"/>
-    </row>
-    <row r="5" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="4">
+        <v>32</v>
+      </c>
+      <c r="AA4" s="8">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA5" s="8"/>
-    </row>
-    <row r="6" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="4">
-        <v>3</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="4">
-        <v>2</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="5">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA6" s="8"/>
-    </row>
-    <row r="7" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="4">
-        <v>2</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="5">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA7" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
